--- a/Fo_Status.xlsx
+++ b/Fo_Status.xlsx
@@ -59,28 +59,28 @@
     <t>20/04/2026 15:16:30</t>
   </si>
   <si>
+    <t>Finished</t>
+  </si>
+  <si>
+    <t>TAPL-A-2779-A</t>
+  </si>
+  <si>
+    <t>WARPSTREME-E-PLUS-218INCH-28GG</t>
+  </si>
+  <si>
+    <t>18/04/2026 18:43:56</t>
+  </si>
+  <si>
     <t>Approved</t>
   </si>
   <si>
-    <t>TAPL-A-2779-A</t>
-  </si>
-  <si>
-    <t>WARPSTREME-E-PLUS-218INCH-28GG</t>
-  </si>
-  <si>
-    <t>0d 0hrs</t>
-  </si>
-  <si>
-    <t>18/04/2026 18:43:56</t>
-  </si>
-  <si>
     <t>TAPL-A-2814</t>
   </si>
   <si>
     <t>WARPSTREME-ALPHA-218INCH-28GG</t>
   </si>
   <si>
-    <t>2d 4hrs</t>
+    <t>2d 6hrs</t>
   </si>
   <si>
     <t>17/04/2026 15:00:18</t>
@@ -92,7 +92,7 @@
     <t>DENSITY-LITE-PLUS-38DIA-30GG</t>
   </si>
   <si>
-    <t>19d 4hrs</t>
+    <t>18d 18hrs</t>
   </si>
   <si>
     <t>15/04/2026 14:54:57</t>
@@ -125,7 +125,7 @@
     <t>NEW CRACKLE 34DIA 32GG</t>
   </si>
   <si>
-    <t>94d 7hrs</t>
+    <t>94d 3hrs</t>
   </si>
   <si>
     <t>08/04/2026 15:01:49</t>
@@ -137,6 +137,9 @@
     <t>UPCORD-FULL-36DIA-28GG</t>
   </si>
   <si>
+    <t>1d 11hrs</t>
+  </si>
+  <si>
     <t>06/04/2026 18:24:05</t>
   </si>
   <si>
@@ -146,402 +149,399 @@
     <t>AURORA 36DIA 28GG</t>
   </si>
   <si>
+    <t>7d 19hrs</t>
+  </si>
+  <si>
+    <t>06/04/2026 18:23:13</t>
+  </si>
+  <si>
+    <t>TAPL-A-2795</t>
+  </si>
+  <si>
+    <t>DC-CAT-MELANGE-30DIA-32GG-V2</t>
+  </si>
+  <si>
+    <t>6d 22hrs</t>
+  </si>
+  <si>
+    <t>06/04/2026 18:22:12</t>
+  </si>
+  <si>
+    <t>TAPL-A-2796</t>
+  </si>
+  <si>
+    <t>CHROMA 34DIA 28GG</t>
+  </si>
+  <si>
+    <t>18d 3hrs</t>
+  </si>
+  <si>
+    <t>06/04/2026 18:21:19</t>
+  </si>
+  <si>
+    <t>TAPL-A-2797</t>
+  </si>
+  <si>
+    <t>MICRODOT SOLID 30DIA 30GG</t>
+  </si>
+  <si>
+    <t>27d 10hrs</t>
+  </si>
+  <si>
+    <t>06/04/2026 18:20:37</t>
+  </si>
+  <si>
+    <t>TAPL-A-2798</t>
+  </si>
+  <si>
+    <t>MICRODOT-SOLID-30DIA-32GG</t>
+  </si>
+  <si>
+    <t>34d 23hrs</t>
+  </si>
+  <si>
+    <t>06/04/2026 11:00:32</t>
+  </si>
+  <si>
+    <t>TAPL-A-2388-B</t>
+  </si>
+  <si>
+    <t>MICRODOT PANT 34DIA 24GG</t>
+  </si>
+  <si>
+    <t>10d 0hrs</t>
+  </si>
+  <si>
+    <t>04/04/2026 18:12:06</t>
+  </si>
+  <si>
+    <t>TAPL-A-2778</t>
+  </si>
+  <si>
+    <t>HYCROSS-38DIA-28GG</t>
+  </si>
+  <si>
+    <t>9d 0hrs</t>
+  </si>
+  <si>
+    <t>04/04/2026 12:00:51</t>
+  </si>
+  <si>
+    <t>TAPL-A-2791</t>
+  </si>
+  <si>
+    <t>04/04/2026 11:54:53</t>
+  </si>
+  <si>
+    <t>TAPL-A-2779</t>
+  </si>
+  <si>
+    <t>03/04/2026 10:42:18</t>
+  </si>
+  <si>
+    <t>TAPL-A-2744</t>
+  </si>
+  <si>
+    <t>ROOTS-38DIA-32GG</t>
+  </si>
+  <si>
+    <t>6d 17hrs</t>
+  </si>
+  <si>
+    <t>02/04/2026 18:39:56</t>
+  </si>
+  <si>
+    <t>TAPL-A-2772</t>
+  </si>
+  <si>
+    <t>02/04/2026 17:26:42</t>
+  </si>
+  <si>
+    <t>TAPL-A-2580</t>
+  </si>
+  <si>
+    <t>WELLKNOWN-PIQUE-28DIA-28GG</t>
+  </si>
+  <si>
+    <t>13d 19hrs</t>
+  </si>
+  <si>
+    <t>31/03/2026 18:47:45</t>
+  </si>
+  <si>
+    <t>TAPL-A-2773</t>
+  </si>
+  <si>
+    <t>CORE FLEX 36DIA 28GG</t>
+  </si>
+  <si>
+    <t>2d 13hrs</t>
+  </si>
+  <si>
+    <t>25/03/2026 13:00:45</t>
+  </si>
+  <si>
+    <t>TAPL-A-2337-B</t>
+  </si>
+  <si>
+    <t>DC CAT MELANGE 30DIA 30GG V-2</t>
+  </si>
+  <si>
+    <t>25/03/2026 12:53:40</t>
+  </si>
+  <si>
+    <t>TAPL-A-2391-A</t>
+  </si>
+  <si>
+    <t>1d 1hrs</t>
+  </si>
+  <si>
+    <t>23/03/2026 11:07:53</t>
+  </si>
+  <si>
+    <t>TAPL-A-2616</t>
+  </si>
+  <si>
+    <t>CRYSTA 36DIA 28GG</t>
+  </si>
+  <si>
+    <t>4d 15hrs</t>
+  </si>
+  <si>
+    <t>23/03/2026 11:06:00</t>
+  </si>
+  <si>
+    <t>TAPL-A-2614</t>
+  </si>
+  <si>
+    <t>WARPSTREME-A2-218INCH-32GG</t>
+  </si>
+  <si>
+    <t>23/03/2026 10:56:48</t>
+  </si>
+  <si>
+    <t>TAPL-A-2606</t>
+  </si>
+  <si>
+    <t>3d 10hrs</t>
+  </si>
+  <si>
+    <t>23/03/2026 10:55:18</t>
+  </si>
+  <si>
+    <t>TAPL-A-2605</t>
+  </si>
+  <si>
+    <t>21/03/2026 08:59:43</t>
+  </si>
+  <si>
+    <t>TAPL-A-2602</t>
+  </si>
+  <si>
+    <t>INTERLOCK LYCRA O/W 36DIA 32GG</t>
+  </si>
+  <si>
+    <t>7d 14hrs</t>
+  </si>
+  <si>
+    <t>18/03/2026 11:13:14</t>
+  </si>
+  <si>
+    <t>TAPL-A-2388-A</t>
+  </si>
+  <si>
+    <t>PANT SOLID 34DIA 24GG</t>
+  </si>
+  <si>
+    <t>16/03/2026 17:31:44</t>
+  </si>
+  <si>
+    <t>TAPL-A-2337-A</t>
+  </si>
+  <si>
+    <t>16/03/2026 09:18:07</t>
+  </si>
+  <si>
+    <t>TAPL-A-2533(IJ-449)</t>
+  </si>
+  <si>
+    <t>CONNECT JACQ 34DIA 30GG</t>
+  </si>
+  <si>
+    <t>3d 23hrs</t>
+  </si>
+  <si>
+    <t>16/03/2026 09:14:44</t>
+  </si>
+  <si>
+    <t>TAPL-A-2534 (IJ-448)</t>
+  </si>
+  <si>
+    <t>6d 4hrs</t>
+  </si>
+  <si>
+    <t>16/03/2026 09:08:00</t>
+  </si>
+  <si>
+    <t>TAPL-A-2522</t>
+  </si>
+  <si>
+    <t>MEMO-34DIA-32GG</t>
+  </si>
+  <si>
+    <t>14/03/2026 20:32:07</t>
+  </si>
+  <si>
+    <t>TAPL-A-2521</t>
+  </si>
+  <si>
+    <t>14/03/2026 19:45:37</t>
+  </si>
+  <si>
+    <t>TAPL-A-2532</t>
+  </si>
+  <si>
+    <t>12/03/2026 09:39:44</t>
+  </si>
+  <si>
+    <t>TAPL-A-2524</t>
+  </si>
+  <si>
+    <t>FEATHERS 34DIA 32GG</t>
+  </si>
+  <si>
+    <t>12/03/2026 09:38:59</t>
+  </si>
+  <si>
+    <t>TAPL-A-2523</t>
+  </si>
+  <si>
+    <t>RITELAM 28DIA 28GG</t>
+  </si>
+  <si>
+    <t>5d 13hrs</t>
+  </si>
+  <si>
+    <t>12/03/2026 09:27:25</t>
+  </si>
+  <si>
+    <t>TAPL-A-2509</t>
+  </si>
+  <si>
+    <t>PLATED-JERSEY-36DIA-28GG-V6</t>
+  </si>
+  <si>
+    <t>2d 0hrs</t>
+  </si>
+  <si>
+    <t>12/03/2026 09:26:48</t>
+  </si>
+  <si>
+    <t>TAPL-A-2507</t>
+  </si>
+  <si>
+    <t>12/03/2026 09:25:52</t>
+  </si>
+  <si>
+    <t>TAPL-A-2508</t>
+  </si>
+  <si>
+    <t>06/03/2026 19:27:17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAPL-A-2452 </t>
+  </si>
+  <si>
+    <t>06/03/2026 19:26:19</t>
+  </si>
+  <si>
+    <t>TAPL-A-2451 (IJ-403)</t>
+  </si>
+  <si>
+    <t>INTERLOCK JACQUARD 34DIA 30GG</t>
+  </si>
+  <si>
+    <t>06/03/2026 19:25:16</t>
+  </si>
+  <si>
+    <t>TAPL-A-2454</t>
+  </si>
+  <si>
+    <t>PANT CAT MELANGE 34DIA 24GG</t>
+  </si>
+  <si>
+    <t>12d 22hrs</t>
+  </si>
+  <si>
+    <t>06/03/2026 19:24:44</t>
+  </si>
+  <si>
+    <t>TAPL-A-2453</t>
+  </si>
+  <si>
+    <t>PANT BLACK MELANGE 34DIA 24GG</t>
+  </si>
+  <si>
+    <t>06/03/2026 19:24:11</t>
+  </si>
+  <si>
+    <t>TAPL-A-2455</t>
+  </si>
+  <si>
+    <t>GREY MELANGE 34DIA 24GG</t>
+  </si>
+  <si>
+    <t>6d 23hrs</t>
+  </si>
+  <si>
+    <t>06/03/2026 19:23:28</t>
+  </si>
+  <si>
+    <t>TAPL-A-2449 (IJ-385)</t>
+  </si>
+  <si>
+    <t>06/03/2026 19:22:32</t>
+  </si>
+  <si>
+    <t>TAPL-A-2450 (IJ-333)</t>
+  </si>
+  <si>
+    <t>06/03/2026 19:21:57</t>
+  </si>
+  <si>
+    <t>TAPL-A-2448 (IJ-162)</t>
+  </si>
+  <si>
+    <t>06/03/2026 18:01:44</t>
+  </si>
+  <si>
+    <t>TAPL-A-2447</t>
+  </si>
+  <si>
+    <t>06/03/2026 11:02:38</t>
+  </si>
+  <si>
+    <t>TAPL-A-2445</t>
+  </si>
+  <si>
+    <t>FLEECE 34DIA 24GG</t>
+  </si>
+  <si>
+    <t>9d 3hrs</t>
+  </si>
+  <si>
+    <t>06/03/2026 11:01:56</t>
+  </si>
+  <si>
+    <t>TAPL-A-2446</t>
+  </si>
+  <si>
+    <t>LEO 36DIA 32GG</t>
+  </si>
+  <si>
     <t>8d 15hrs</t>
   </si>
   <si>
-    <t>06/04/2026 18:23:13</t>
-  </si>
-  <si>
-    <t>TAPL-A-2795</t>
-  </si>
-  <si>
-    <t>DC-CAT-MELANGE-30DIA-32GG-V2</t>
-  </si>
-  <si>
-    <t>7d 11hrs</t>
-  </si>
-  <si>
-    <t>06/04/2026 18:22:12</t>
-  </si>
-  <si>
-    <t>TAPL-A-2796</t>
-  </si>
-  <si>
-    <t>CHROMA 34DIA 28GG</t>
-  </si>
-  <si>
-    <t>18d 3hrs</t>
-  </si>
-  <si>
-    <t>06/04/2026 18:21:19</t>
-  </si>
-  <si>
-    <t>TAPL-A-2797</t>
-  </si>
-  <si>
-    <t>MICRODOT SOLID 30DIA 30GG</t>
-  </si>
-  <si>
-    <t>27d 21hrs</t>
-  </si>
-  <si>
-    <t>06/04/2026 18:20:37</t>
-  </si>
-  <si>
-    <t>TAPL-A-2798</t>
-  </si>
-  <si>
-    <t>MICRODOT-SOLID-30DIA-32GG</t>
-  </si>
-  <si>
-    <t>35d 19hrs</t>
-  </si>
-  <si>
-    <t>06/04/2026 11:00:32</t>
-  </si>
-  <si>
-    <t>TAPL-A-2388-B</t>
-  </si>
-  <si>
-    <t>MICRODOT PANT 34DIA 24GG</t>
-  </si>
-  <si>
-    <t>10d 0hrs</t>
-  </si>
-  <si>
-    <t>04/04/2026 18:12:06</t>
-  </si>
-  <si>
-    <t>TAPL-A-2778</t>
-  </si>
-  <si>
-    <t>HYCROSS-38DIA-28GG</t>
-  </si>
-  <si>
-    <t>9d 12hrs</t>
-  </si>
-  <si>
-    <t>04/04/2026 12:00:51</t>
-  </si>
-  <si>
-    <t>Finished</t>
-  </si>
-  <si>
-    <t>TAPL-A-2791</t>
-  </si>
-  <si>
-    <t>04/04/2026 11:54:53</t>
-  </si>
-  <si>
-    <t>TAPL-A-2779</t>
-  </si>
-  <si>
-    <t>03/04/2026 10:42:18</t>
-  </si>
-  <si>
-    <t>TAPL-A-2744</t>
-  </si>
-  <si>
-    <t>ROOTS-38DIA-32GG</t>
-  </si>
-  <si>
-    <t>7d 12hrs</t>
-  </si>
-  <si>
-    <t>02/04/2026 18:39:56</t>
-  </si>
-  <si>
-    <t>TAPL-A-2772</t>
-  </si>
-  <si>
-    <t>02/04/2026 17:26:42</t>
-  </si>
-  <si>
-    <t>TAPL-A-2580</t>
-  </si>
-  <si>
-    <t>WELLKNOWN-PIQUE-28DIA-28GG</t>
-  </si>
-  <si>
-    <t>13d 19hrs</t>
-  </si>
-  <si>
-    <t>31/03/2026 18:47:45</t>
-  </si>
-  <si>
-    <t>TAPL-A-2773</t>
-  </si>
-  <si>
-    <t>CORE FLEX 36DIA 28GG</t>
-  </si>
-  <si>
-    <t>3d 8hrs</t>
-  </si>
-  <si>
-    <t>25/03/2026 13:00:45</t>
-  </si>
-  <si>
-    <t>TAPL-A-2337-B</t>
-  </si>
-  <si>
-    <t>DC CAT MELANGE 30DIA 30GG V-2</t>
-  </si>
-  <si>
-    <t>25/03/2026 12:53:40</t>
-  </si>
-  <si>
-    <t>TAPL-A-2391-A</t>
-  </si>
-  <si>
-    <t>1d 13hrs</t>
-  </si>
-  <si>
-    <t>23/03/2026 11:07:53</t>
-  </si>
-  <si>
-    <t>TAPL-A-2616</t>
-  </si>
-  <si>
-    <t>CRYSTA 36DIA 28GG</t>
-  </si>
-  <si>
-    <t>5d 5hrs</t>
-  </si>
-  <si>
-    <t>23/03/2026 11:06:00</t>
-  </si>
-  <si>
-    <t>TAPL-A-2614</t>
-  </si>
-  <si>
-    <t>WARPSTREME-A2-218INCH-32GG</t>
-  </si>
-  <si>
-    <t>23/03/2026 10:56:48</t>
-  </si>
-  <si>
-    <t>TAPL-A-2606</t>
-  </si>
-  <si>
-    <t>4d 3hrs</t>
-  </si>
-  <si>
-    <t>23/03/2026 10:55:18</t>
-  </si>
-  <si>
-    <t>TAPL-A-2605</t>
-  </si>
-  <si>
-    <t>21/03/2026 08:59:43</t>
-  </si>
-  <si>
-    <t>TAPL-A-2602</t>
-  </si>
-  <si>
-    <t>INTERLOCK LYCRA O/W 36DIA 32GG</t>
-  </si>
-  <si>
-    <t>8d 3hrs</t>
-  </si>
-  <si>
-    <t>18/03/2026 11:13:14</t>
-  </si>
-  <si>
-    <t>TAPL-A-2388-A</t>
-  </si>
-  <si>
-    <t>PANT SOLID 34DIA 24GG</t>
-  </si>
-  <si>
-    <t>16/03/2026 17:31:44</t>
-  </si>
-  <si>
-    <t>TAPL-A-2337-A</t>
-  </si>
-  <si>
-    <t>16/03/2026 09:18:07</t>
-  </si>
-  <si>
-    <t>TAPL-A-2533(IJ-449)</t>
-  </si>
-  <si>
-    <t>CONNECT JACQ 34DIA 30GG</t>
-  </si>
-  <si>
-    <t>4d 16hrs</t>
-  </si>
-  <si>
-    <t>16/03/2026 09:14:44</t>
-  </si>
-  <si>
-    <t>TAPL-A-2534 (IJ-448)</t>
-  </si>
-  <si>
-    <t>6d 20hrs</t>
-  </si>
-  <si>
-    <t>16/03/2026 09:08:00</t>
-  </si>
-  <si>
-    <t>TAPL-A-2522</t>
-  </si>
-  <si>
-    <t>MEMO-34DIA-32GG</t>
-  </si>
-  <si>
-    <t>14/03/2026 20:32:07</t>
-  </si>
-  <si>
-    <t>TAPL-A-2521</t>
-  </si>
-  <si>
-    <t>14/03/2026 19:45:37</t>
-  </si>
-  <si>
-    <t>TAPL-A-2532</t>
-  </si>
-  <si>
-    <t>12/03/2026 09:39:44</t>
-  </si>
-  <si>
-    <t>TAPL-A-2524</t>
-  </si>
-  <si>
-    <t>FEATHERS 34DIA 32GG</t>
-  </si>
-  <si>
-    <t>12/03/2026 09:38:59</t>
-  </si>
-  <si>
-    <t>TAPL-A-2523</t>
-  </si>
-  <si>
-    <t>RITELAM 28DIA 28GG</t>
-  </si>
-  <si>
-    <t>5d 13hrs</t>
-  </si>
-  <si>
-    <t>12/03/2026 09:27:25</t>
-  </si>
-  <si>
-    <t>TAPL-A-2509</t>
-  </si>
-  <si>
-    <t>PLATED-JERSEY-36DIA-28GG-V6</t>
-  </si>
-  <si>
-    <t>2d 16hrs</t>
-  </si>
-  <si>
-    <t>12/03/2026 09:26:48</t>
-  </si>
-  <si>
-    <t>TAPL-A-2507</t>
-  </si>
-  <si>
-    <t>12/03/2026 09:25:52</t>
-  </si>
-  <si>
-    <t>TAPL-A-2508</t>
-  </si>
-  <si>
-    <t>06/03/2026 19:27:17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAPL-A-2452 </t>
-  </si>
-  <si>
-    <t>06/03/2026 19:26:19</t>
-  </si>
-  <si>
-    <t>TAPL-A-2451 (IJ-403)</t>
-  </si>
-  <si>
-    <t>INTERLOCK JACQUARD 34DIA 30GG</t>
-  </si>
-  <si>
-    <t>06/03/2026 19:25:16</t>
-  </si>
-  <si>
-    <t>TAPL-A-2454</t>
-  </si>
-  <si>
-    <t>PANT CAT MELANGE 34DIA 24GG</t>
-  </si>
-  <si>
-    <t>13d 9hrs</t>
-  </si>
-  <si>
-    <t>06/03/2026 19:24:44</t>
-  </si>
-  <si>
-    <t>TAPL-A-2453</t>
-  </si>
-  <si>
-    <t>PANT BLACK MELANGE 34DIA 24GG</t>
-  </si>
-  <si>
-    <t>06/03/2026 19:24:11</t>
-  </si>
-  <si>
-    <t>TAPL-A-2455</t>
-  </si>
-  <si>
-    <t>GREY MELANGE 34DIA 24GG</t>
-  </si>
-  <si>
-    <t>7d 7hrs</t>
-  </si>
-  <si>
-    <t>06/03/2026 19:23:28</t>
-  </si>
-  <si>
-    <t>TAPL-A-2449 (IJ-385)</t>
-  </si>
-  <si>
-    <t>06/03/2026 19:22:32</t>
-  </si>
-  <si>
-    <t>TAPL-A-2450 (IJ-333)</t>
-  </si>
-  <si>
-    <t>06/03/2026 19:21:57</t>
-  </si>
-  <si>
-    <t>TAPL-A-2448 (IJ-162)</t>
-  </si>
-  <si>
-    <t>06/03/2026 18:01:44</t>
-  </si>
-  <si>
-    <t>TAPL-A-2447</t>
-  </si>
-  <si>
-    <t>06/03/2026 11:02:38</t>
-  </si>
-  <si>
-    <t>TAPL-A-2445</t>
-  </si>
-  <si>
-    <t>FLEECE 34DIA 24GG</t>
-  </si>
-  <si>
-    <t>9d 14hrs</t>
-  </si>
-  <si>
-    <t>06/03/2026 11:01:56</t>
-  </si>
-  <si>
-    <t>TAPL-A-2446</t>
-  </si>
-  <si>
-    <t>LEO 36DIA 32GG</t>
-  </si>
-  <si>
-    <t>8d 21hrs</t>
-  </si>
-  <si>
     <t>05/03/2026 12:37:26</t>
   </si>
   <si>
@@ -560,7 +560,7 @@
     <t>TAPL-A-2389</t>
   </si>
   <si>
-    <t>3d 10hrs</t>
+    <t>2d 8hrs</t>
   </si>
   <si>
     <t>24/02/2026 12:40:19</t>
@@ -674,7 +674,7 @@
     <t>CALLISTO 36DIA 28GG</t>
   </si>
   <si>
-    <t>7d 17hrs</t>
+    <t>7d 0hrs</t>
   </si>
   <si>
     <t>12/02/2026 10:25:38</t>
@@ -716,7 +716,7 @@
     <t>DISCORD BEY 36DIA 32GG</t>
   </si>
   <si>
-    <t>11d 17hrs</t>
+    <t>15d 2hrs</t>
   </si>
   <si>
     <t>10/02/2026 11:25:11</t>
@@ -3472,19 +3472,15 @@
       <c r="K2" s="4">
         <v>0.1</v>
       </c>
-      <c r="L2" s="4">
-        <v>550</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>17</v>
-      </c>
+      <c r="L2" s="4"/>
+      <c r="M2" s="3"/>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>14</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>19</v>
@@ -3499,22 +3495,22 @@
         <v>50400</v>
       </c>
       <c r="G3" s="5">
-        <v>2700</v>
+        <v>4740</v>
       </c>
       <c r="H3" s="4">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="I3" s="5">
-        <v>1505.52</v>
+        <v>2223.82</v>
       </c>
       <c r="J3" s="4">
-        <v>1630</v>
+        <v>1606</v>
       </c>
       <c r="K3" s="4">
-        <v>1194.48</v>
+        <v>2516.18</v>
       </c>
       <c r="L3" s="4">
-        <v>550</v>
+        <v>1100</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>21</v>
@@ -3525,7 +3521,7 @@
         <v>22</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>23</v>
@@ -3543,16 +3539,16 @@
         <v>2500</v>
       </c>
       <c r="H4" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I4" s="5">
-        <v>100</v>
+        <v>151.48</v>
       </c>
       <c r="J4" s="4">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="K4" s="4">
-        <v>2400</v>
+        <v>2348.52</v>
       </c>
       <c r="L4" s="4">
         <v>125</v>
@@ -3566,7 +3562,7 @@
         <v>26</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>27</v>
@@ -3607,7 +3603,7 @@
         <v>30</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>31</v>
@@ -3648,7 +3644,7 @@
         <v>33</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>34</v>
@@ -3666,16 +3662,16 @@
         <v>15000</v>
       </c>
       <c r="H7" s="4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I7" s="5">
-        <v>853.5</v>
+        <v>878.58</v>
       </c>
       <c r="J7" s="4">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="K7" s="4">
-        <v>14146.5</v>
+        <v>14121.42</v>
       </c>
       <c r="L7" s="4">
         <v>150</v>
@@ -3689,7 +3685,7 @@
         <v>37</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>38</v>
@@ -3707,36 +3703,36 @@
         <v>2500</v>
       </c>
       <c r="H8" s="4">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I8" s="5">
-        <v>1956.78</v>
+        <v>2132.44</v>
       </c>
       <c r="J8" s="4">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="K8" s="4">
-        <v>543.22</v>
+        <v>367.56</v>
       </c>
       <c r="L8" s="4">
         <v>250</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E9" s="4">
         <v>1309</v>
@@ -3748,36 +3744,36 @@
         <v>5000</v>
       </c>
       <c r="H9" s="4">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="I9" s="5">
-        <v>1548.48</v>
+        <v>1874.4</v>
       </c>
       <c r="J9" s="4">
-        <v>1247</v>
+        <v>1234</v>
       </c>
       <c r="K9" s="4">
-        <v>3451.52</v>
+        <v>3125.6</v>
       </c>
       <c r="L9" s="4">
         <v>400</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E10" s="4">
         <v>2457</v>
@@ -3789,36 +3785,36 @@
         <v>10000</v>
       </c>
       <c r="H10" s="4">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="I10" s="5">
-        <v>1003.26</v>
+        <v>1651.68</v>
       </c>
       <c r="J10" s="4">
-        <v>2417</v>
+        <v>2391</v>
       </c>
       <c r="K10" s="4">
-        <v>8996.74</v>
+        <v>8348.32</v>
       </c>
       <c r="L10" s="4">
         <v>1200</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E11" s="4">
         <v>288</v>
@@ -3845,21 +3841,21 @@
         <v>300</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E12" s="4">
         <v>1400</v>
@@ -3871,36 +3867,36 @@
         <v>7500</v>
       </c>
       <c r="H12" s="4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I12" s="5">
-        <v>521.4</v>
+        <v>645.62</v>
       </c>
       <c r="J12" s="4">
-        <v>1379</v>
+        <v>1374</v>
       </c>
       <c r="K12" s="4">
-        <v>6978.6</v>
+        <v>6854.38</v>
       </c>
       <c r="L12" s="4">
         <v>250</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E13" s="4">
         <v>1400</v>
@@ -3912,36 +3908,36 @@
         <v>20000</v>
       </c>
       <c r="H13" s="4">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="I13" s="5">
-        <v>9258.62</v>
+        <v>9506.2</v>
       </c>
       <c r="J13" s="4">
-        <v>1028</v>
+        <v>1018</v>
       </c>
       <c r="K13" s="4">
-        <v>10741.38</v>
+        <v>10493.8</v>
       </c>
       <c r="L13" s="4">
         <v>300</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E14" s="4">
         <v>1773</v>
@@ -3968,21 +3964,21 @@
         <v>2400</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E15" s="4">
         <v>1920</v>
@@ -3994,30 +3990,30 @@
         <v>14225</v>
       </c>
       <c r="H15" s="4">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="I15" s="5">
-        <v>4244.68</v>
+        <v>4744.48</v>
       </c>
       <c r="J15" s="4">
-        <v>1751</v>
+        <v>1731</v>
       </c>
       <c r="K15" s="4">
-        <v>9980.32</v>
+        <v>9480.52</v>
       </c>
       <c r="L15" s="4">
         <v>1050</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>70</v>
@@ -4054,7 +4050,7 @@
         <v>71</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>72</v>
@@ -4091,7 +4087,7 @@
         <v>73</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>74</v>
@@ -4109,16 +4105,16 @@
         <v>7200</v>
       </c>
       <c r="H18" s="4">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="I18" s="5">
-        <v>4759.86</v>
+        <v>5009.92</v>
       </c>
       <c r="J18" s="4">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="K18" s="4">
-        <v>2440.14</v>
+        <v>2190.08</v>
       </c>
       <c r="L18" s="4">
         <v>325</v>
@@ -4132,7 +4128,7 @@
         <v>77</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>78</v>
@@ -4169,7 +4165,7 @@
         <v>79</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>80</v>
@@ -4210,7 +4206,7 @@
         <v>83</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>84</v>
@@ -4228,16 +4224,16 @@
         <v>1250</v>
       </c>
       <c r="H21" s="4">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I21" s="5">
-        <v>832.84</v>
+        <v>931.94</v>
       </c>
       <c r="J21" s="4">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="K21" s="4">
-        <v>417.16</v>
+        <v>318.06</v>
       </c>
       <c r="L21" s="4">
         <v>125</v>
@@ -4251,7 +4247,7 @@
         <v>87</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>88</v>
@@ -4288,13 +4284,13 @@
         <v>90</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>91</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E23" s="4">
         <v>121</v>
@@ -4306,16 +4302,16 @@
         <v>3025</v>
       </c>
       <c r="H23" s="4">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="I23" s="5">
-        <v>2245.62</v>
+        <v>2498.32</v>
       </c>
       <c r="J23" s="4">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="K23" s="4">
-        <v>779.38</v>
+        <v>526.68</v>
       </c>
       <c r="L23" s="4">
         <v>500</v>
@@ -4329,7 +4325,7 @@
         <v>93</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>94</v>
@@ -4347,16 +4343,16 @@
         <v>8650</v>
       </c>
       <c r="H24" s="4">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="I24" s="5">
-        <v>6683.68</v>
+        <v>6909.68</v>
       </c>
       <c r="J24" s="4">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="K24" s="4">
-        <v>1966.32</v>
+        <v>1740.32</v>
       </c>
       <c r="L24" s="4">
         <v>375</v>
@@ -4370,7 +4366,7 @@
         <v>97</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>98</v>
@@ -4407,7 +4403,7 @@
         <v>100</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>101</v>
@@ -4425,16 +4421,16 @@
         <v>9000</v>
       </c>
       <c r="H26" s="4">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="I26" s="5">
-        <v>2139.18</v>
+        <v>3342.44</v>
       </c>
       <c r="J26" s="4">
-        <v>505</v>
+        <v>465</v>
       </c>
       <c r="K26" s="4">
-        <v>6860.82</v>
+        <v>5657.56</v>
       </c>
       <c r="L26" s="4">
         <v>1650</v>
@@ -4448,7 +4444,7 @@
         <v>103</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>104</v>
@@ -4485,7 +4481,7 @@
         <v>105</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>106</v>
@@ -4503,16 +4499,16 @@
         <v>9000</v>
       </c>
       <c r="H28" s="4">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="I28" s="5">
-        <v>6552.24</v>
+        <v>6724.78</v>
       </c>
       <c r="J28" s="4">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="K28" s="4">
-        <v>2447.76</v>
+        <v>2275.22</v>
       </c>
       <c r="L28" s="4">
         <v>300</v>
@@ -4526,7 +4522,7 @@
         <v>109</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>110</v>
@@ -4563,7 +4559,7 @@
         <v>112</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>113</v>
@@ -4600,7 +4596,7 @@
         <v>114</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>115</v>
@@ -4618,16 +4614,16 @@
         <v>2400</v>
       </c>
       <c r="H31" s="4">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="I31" s="5">
-        <v>1577.22</v>
+        <v>1703.42</v>
       </c>
       <c r="J31" s="4">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K31" s="4">
-        <v>822.78</v>
+        <v>696.58</v>
       </c>
       <c r="L31" s="4">
         <v>175</v>
@@ -4641,7 +4637,7 @@
         <v>118</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>119</v>
@@ -4659,16 +4655,16 @@
         <v>2400</v>
       </c>
       <c r="H32" s="4">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="I32" s="5">
-        <v>1374.68</v>
+        <v>1474.42</v>
       </c>
       <c r="J32" s="4">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="K32" s="4">
-        <v>1025.32</v>
+        <v>925.58</v>
       </c>
       <c r="L32" s="4">
         <v>150</v>
@@ -4682,7 +4678,7 @@
         <v>121</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>122</v>
@@ -4719,7 +4715,7 @@
         <v>124</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>125</v>
@@ -4756,7 +4752,7 @@
         <v>126</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>127</v>
@@ -4793,7 +4789,7 @@
         <v>128</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>129</v>
@@ -4811,16 +4807,16 @@
         <v>4800</v>
       </c>
       <c r="H36" s="4">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="I36" s="5">
-        <v>3183.78</v>
+        <v>3233.74</v>
       </c>
       <c r="J36" s="4">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K36" s="4">
-        <v>1616.22</v>
+        <v>1566.26</v>
       </c>
       <c r="L36" s="4">
         <v>0</v>
@@ -4832,7 +4828,7 @@
         <v>131</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>132</v>
@@ -4873,7 +4869,7 @@
         <v>135</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>136</v>
@@ -4891,16 +4887,16 @@
         <v>12800</v>
       </c>
       <c r="H38" s="4">
-        <v>392</v>
+        <v>422</v>
       </c>
       <c r="I38" s="5">
-        <v>9835.3</v>
+        <v>10587.66</v>
       </c>
       <c r="J38" s="4">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="K38" s="4">
-        <v>2964.7</v>
+        <v>2212.34</v>
       </c>
       <c r="L38" s="4">
         <v>1100</v>
@@ -4914,7 +4910,7 @@
         <v>139</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>140</v>
@@ -4951,7 +4947,7 @@
         <v>141</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>142</v>
@@ -4988,7 +4984,7 @@
         <v>143</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>144</v>
@@ -5025,7 +5021,7 @@
         <v>145</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>146</v>
@@ -5062,7 +5058,7 @@
         <v>148</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>149</v>
@@ -5080,16 +5076,16 @@
         <v>4800</v>
       </c>
       <c r="H43" s="4">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="I43" s="5">
-        <v>2458.82</v>
+        <v>2533.88</v>
       </c>
       <c r="J43" s="4">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="K43" s="4">
-        <v>2341.18</v>
+        <v>2266.12</v>
       </c>
       <c r="L43" s="4">
         <v>175</v>
@@ -5103,7 +5099,7 @@
         <v>152</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>153</v>
@@ -5140,7 +5136,7 @@
         <v>155</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>156</v>
@@ -5158,16 +5154,16 @@
         <v>1600</v>
       </c>
       <c r="H45" s="4">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I45" s="5">
-        <v>502.22</v>
+        <v>552.6</v>
       </c>
       <c r="J45" s="4">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K45" s="4">
-        <v>1097.78</v>
+        <v>1047.4</v>
       </c>
       <c r="L45" s="4">
         <v>150</v>
@@ -5181,7 +5177,7 @@
         <v>159</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>160</v>
@@ -5218,7 +5214,7 @@
         <v>161</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>162</v>
@@ -5255,7 +5251,7 @@
         <v>163</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>164</v>
@@ -5292,7 +5288,7 @@
         <v>165</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>166</v>
@@ -5329,7 +5325,7 @@
         <v>167</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>168</v>
@@ -5344,19 +5340,19 @@
         <v>36000</v>
       </c>
       <c r="G50" s="5">
-        <v>32300</v>
+        <v>32400</v>
       </c>
       <c r="H50" s="4">
-        <v>1000</v>
+        <v>1018</v>
       </c>
       <c r="I50" s="5">
-        <v>25106.82</v>
+        <v>25555.2</v>
       </c>
       <c r="J50" s="4">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="K50" s="4">
-        <v>7193.18</v>
+        <v>6844.8</v>
       </c>
       <c r="L50" s="4">
         <v>750</v>
@@ -5370,7 +5366,7 @@
         <v>171</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>172</v>
@@ -5388,16 +5384,16 @@
         <v>7350</v>
       </c>
       <c r="H51" s="4">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I51" s="5">
-        <v>5572</v>
+        <v>5621.88</v>
       </c>
       <c r="J51" s="4">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="K51" s="4">
-        <v>1778</v>
+        <v>1728.12</v>
       </c>
       <c r="L51" s="4">
         <v>200</v>
@@ -5411,7 +5407,7 @@
         <v>175</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>176</v>
@@ -5452,13 +5448,13 @@
         <v>179</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>180</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E53" s="4">
         <v>704</v>
@@ -5470,16 +5466,16 @@
         <v>17600</v>
       </c>
       <c r="H53" s="4">
-        <v>659</v>
+        <v>672</v>
       </c>
       <c r="I53" s="5">
-        <v>16569.02</v>
+        <v>16896.68</v>
       </c>
       <c r="J53" s="4">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="K53" s="4">
-        <v>1030.98</v>
+        <v>703.32</v>
       </c>
       <c r="L53" s="4">
         <v>300</v>
@@ -5493,13 +5489,13 @@
         <v>182</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>183</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E54" s="4">
         <v>609</v>
@@ -5530,13 +5526,13 @@
         <v>184</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>185</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E55" s="4">
         <v>112</v>
@@ -5567,13 +5563,13 @@
         <v>186</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>187</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E56" s="4">
         <v>1131</v>
@@ -5604,7 +5600,7 @@
         <v>188</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>189</v>
@@ -5641,7 +5637,7 @@
         <v>191</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>192</v>
@@ -5678,7 +5674,7 @@
         <v>193</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>194</v>
@@ -5715,7 +5711,7 @@
         <v>195</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>196</v>
@@ -5752,7 +5748,7 @@
         <v>197</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>198</v>
@@ -5789,7 +5785,7 @@
         <v>199</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>200</v>
@@ -5826,7 +5822,7 @@
         <v>201</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>202</v>
@@ -5863,7 +5859,7 @@
         <v>203</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>204</v>
@@ -5900,7 +5896,7 @@
         <v>205</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>206</v>
@@ -5937,7 +5933,7 @@
         <v>207</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>208</v>
@@ -5974,7 +5970,7 @@
         <v>209</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>210</v>
@@ -6011,7 +6007,7 @@
         <v>211</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>212</v>
@@ -6048,7 +6044,7 @@
         <v>214</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>215</v>
@@ -6085,7 +6081,7 @@
         <v>216</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>217</v>
@@ -6103,16 +6099,16 @@
         <v>17820</v>
       </c>
       <c r="H70" s="4">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="I70" s="5">
-        <v>15884.86</v>
+        <v>16065.1</v>
       </c>
       <c r="J70" s="4">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="K70" s="4">
-        <v>1935.14</v>
+        <v>1754.9</v>
       </c>
       <c r="L70" s="4">
         <v>250</v>
@@ -6126,7 +6122,7 @@
         <v>220</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>221</v>
@@ -6163,7 +6159,7 @@
         <v>223</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>224</v>
@@ -6200,7 +6196,7 @@
         <v>226</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>227</v>
@@ -6237,7 +6233,7 @@
         <v>228</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>229</v>
@@ -6274,7 +6270,7 @@
         <v>230</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>231</v>
@@ -6289,19 +6285,19 @@
         <v>8300</v>
       </c>
       <c r="G75" s="5">
-        <v>7475</v>
+        <v>8300</v>
       </c>
       <c r="H75" s="4">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="I75" s="5">
-        <v>5130.04</v>
+        <v>5279.52</v>
       </c>
       <c r="J75" s="4">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="K75" s="4">
-        <v>2344.96</v>
+        <v>3020.48</v>
       </c>
       <c r="L75" s="4">
         <v>200</v>
@@ -6315,7 +6311,7 @@
         <v>234</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>235</v>
@@ -6352,13 +6348,13 @@
         <v>237</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>238</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E77" s="4">
         <v>16</v>
@@ -6389,7 +6385,7 @@
         <v>239</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>240</v>
@@ -6426,7 +6422,7 @@
         <v>241</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>242</v>
@@ -6463,7 +6459,7 @@
         <v>243</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>244</v>
@@ -6500,13 +6496,13 @@
         <v>245</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>246</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E81" s="4">
         <v>770</v>
@@ -6537,7 +6533,7 @@
         <v>247</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>248</v>
@@ -6574,7 +6570,7 @@
         <v>249</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>250</v>
@@ -6611,7 +6607,7 @@
         <v>251</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>252</v>
@@ -6652,13 +6648,13 @@
         <v>255</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>256</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E85" s="4">
         <v>60</v>
@@ -6689,7 +6685,7 @@
         <v>257</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>258</v>
@@ -6726,7 +6722,7 @@
         <v>259</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>260</v>
@@ -6763,7 +6759,7 @@
         <v>261</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>262</v>
@@ -6800,7 +6796,7 @@
         <v>263</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>264</v>
@@ -6837,7 +6833,7 @@
         <v>265</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>266</v>
@@ -6874,7 +6870,7 @@
         <v>267</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>268</v>
@@ -6911,7 +6907,7 @@
         <v>269</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>270</v>
@@ -6948,7 +6944,7 @@
         <v>271</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>272</v>
@@ -6985,7 +6981,7 @@
         <v>274</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>275</v>
@@ -7022,7 +7018,7 @@
         <v>276</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>277</v>
@@ -7059,7 +7055,7 @@
         <v>278</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>279</v>
@@ -7096,7 +7092,7 @@
         <v>281</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C97" s="3" t="s">
         <v>282</v>
@@ -7133,7 +7129,7 @@
         <v>283</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C98" s="3" t="s">
         <v>284</v>
@@ -7170,7 +7166,7 @@
         <v>285</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C99" s="3" t="s">
         <v>286</v>
@@ -7207,7 +7203,7 @@
         <v>287</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C100" s="3" t="s">
         <v>288</v>
@@ -7244,7 +7240,7 @@
         <v>289</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C101" s="3" t="s">
         <v>290</v>
@@ -7281,7 +7277,7 @@
         <v>291</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C102" s="3" t="s">
         <v>292</v>
@@ -7318,7 +7314,7 @@
         <v>294</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C103" s="3" t="s">
         <v>295</v>
@@ -7355,7 +7351,7 @@
         <v>296</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C104" s="3" t="s">
         <v>297</v>
@@ -7392,7 +7388,7 @@
         <v>299</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C105" s="3" t="s">
         <v>300</v>
@@ -7429,7 +7425,7 @@
         <v>301</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C106" s="3" t="s">
         <v>302</v>
@@ -7466,7 +7462,7 @@
         <v>304</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>305</v>
@@ -7503,7 +7499,7 @@
         <v>306</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C108" s="3" t="s">
         <v>307</v>
@@ -7540,7 +7536,7 @@
         <v>308</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C109" s="3" t="s">
         <v>309</v>
@@ -7577,7 +7573,7 @@
         <v>310</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C110" s="3" t="s">
         <v>311</v>
@@ -7614,7 +7610,7 @@
         <v>312</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C111" s="3" t="s">
         <v>313</v>
@@ -7651,7 +7647,7 @@
         <v>314</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C112" s="3" t="s">
         <v>315</v>
@@ -7688,7 +7684,7 @@
         <v>316</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C113" s="3" t="s">
         <v>317</v>
@@ -7725,7 +7721,7 @@
         <v>318</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C114" s="3" t="s">
         <v>319</v>
@@ -7762,7 +7758,7 @@
         <v>320</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C115" s="3" t="s">
         <v>321</v>
@@ -7799,7 +7795,7 @@
         <v>322</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C116" s="3" t="s">
         <v>323</v>
@@ -7836,7 +7832,7 @@
         <v>324</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C117" s="3" t="s">
         <v>325</v>
@@ -7873,7 +7869,7 @@
         <v>326</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C118" s="3" t="s">
         <v>327</v>
@@ -7910,7 +7906,7 @@
         <v>328</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C119" s="3" t="s">
         <v>329</v>
@@ -7947,7 +7943,7 @@
         <v>330</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C120" s="3" t="s">
         <v>331</v>
@@ -7984,13 +7980,13 @@
         <v>332</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C121" s="3" t="s">
         <v>333</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E121" s="4">
         <v>288</v>
@@ -8021,7 +8017,7 @@
         <v>334</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C122" s="3" t="s">
         <v>335</v>
@@ -8058,7 +8054,7 @@
         <v>336</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C123" s="3" t="s">
         <v>337</v>
@@ -8095,7 +8091,7 @@
         <v>338</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C124" s="3" t="s">
         <v>339</v>
@@ -8132,7 +8128,7 @@
         <v>340</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C125" s="3" t="s">
         <v>341</v>
@@ -8169,7 +8165,7 @@
         <v>343</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C126" s="3" t="s">
         <v>344</v>
@@ -8206,7 +8202,7 @@
         <v>345</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C127" s="3" t="s">
         <v>346</v>
@@ -8243,7 +8239,7 @@
         <v>347</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C128" s="3" t="s">
         <v>348</v>
@@ -8280,7 +8276,7 @@
         <v>350</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C129" s="3" t="s">
         <v>351</v>
@@ -8317,13 +8313,13 @@
         <v>352</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C130" s="3" t="s">
         <v>353</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E130" s="4">
         <v>32</v>
@@ -8354,13 +8350,13 @@
         <v>354</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C131" s="3" t="s">
         <v>355</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E131" s="4">
         <v>96</v>
@@ -8391,13 +8387,13 @@
         <v>356</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C132" s="3" t="s">
         <v>357</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E132" s="4">
         <v>770</v>
@@ -8428,7 +8424,7 @@
         <v>358</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C133" s="3" t="s">
         <v>359</v>
@@ -8465,7 +8461,7 @@
         <v>360</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C134" s="3" t="s">
         <v>361</v>
@@ -8502,7 +8498,7 @@
         <v>362</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C135" s="3" t="s">
         <v>363</v>
@@ -8539,7 +8535,7 @@
         <v>364</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C136" s="3" t="s">
         <v>365</v>
@@ -8576,13 +8572,13 @@
         <v>367</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C137" s="3" t="s">
         <v>368</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E137" s="4">
         <v>192</v>
@@ -8613,7 +8609,7 @@
         <v>369</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C138" s="3" t="s">
         <v>370</v>
@@ -8650,13 +8646,13 @@
         <v>371</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C139" s="3" t="s">
         <v>372</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E139" s="4">
         <v>3840</v>
@@ -8687,7 +8683,7 @@
         <v>373</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C140" s="3" t="s">
         <v>374</v>
@@ -8724,7 +8720,7 @@
         <v>375</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C141" s="3" t="s">
         <v>376</v>
@@ -8761,7 +8757,7 @@
         <v>378</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C142" s="3" t="s">
         <v>379</v>
@@ -8798,7 +8794,7 @@
         <v>380</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C143" s="3" t="s">
         <v>381</v>
@@ -8835,7 +8831,7 @@
         <v>382</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C144" s="3" t="s">
         <v>383</v>
@@ -8872,7 +8868,7 @@
         <v>385</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C145" s="3" t="s">
         <v>386</v>
@@ -8909,7 +8905,7 @@
         <v>388</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C146" s="3" t="s">
         <v>389</v>
@@ -8946,13 +8942,13 @@
         <v>391</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C147" s="3" t="s">
         <v>392</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E147" s="4">
         <v>413</v>
@@ -8983,7 +8979,7 @@
         <v>393</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C148" s="3" t="s">
         <v>394</v>
@@ -9020,7 +9016,7 @@
         <v>395</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C149" s="3" t="s">
         <v>396</v>
@@ -9057,7 +9053,7 @@
         <v>397</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C150" s="3" t="s">
         <v>398</v>
@@ -9094,7 +9090,7 @@
         <v>399</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C151" s="3" t="s">
         <v>400</v>
@@ -9131,7 +9127,7 @@
         <v>401</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C152" s="3" t="s">
         <v>402</v>
@@ -9168,7 +9164,7 @@
         <v>403</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C153" s="3" t="s">
         <v>404</v>
@@ -9205,7 +9201,7 @@
         <v>405</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C154" s="3" t="s">
         <v>406</v>
@@ -9242,7 +9238,7 @@
         <v>407</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C155" s="3" t="s">
         <v>408</v>
@@ -9279,7 +9275,7 @@
         <v>409</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C156" s="3" t="s">
         <v>410</v>
@@ -9316,7 +9312,7 @@
         <v>411</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C157" s="3" t="s">
         <v>412</v>
@@ -9353,7 +9349,7 @@
         <v>413</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C158" s="3" t="s">
         <v>414</v>
@@ -9390,7 +9386,7 @@
         <v>415</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C159" s="3" t="s">
         <v>416</v>
@@ -9427,13 +9423,13 @@
         <v>417</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C160" s="3" t="s">
         <v>418</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E160" s="4">
         <v>193</v>
@@ -9464,7 +9460,7 @@
         <v>419</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C161" s="3" t="s">
         <v>420</v>
@@ -9501,7 +9497,7 @@
         <v>421</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C162" s="3" t="s">
         <v>422</v>
@@ -9538,7 +9534,7 @@
         <v>424</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C163" s="3" t="s">
         <v>425</v>
@@ -9575,13 +9571,13 @@
         <v>426</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C164" s="3" t="s">
         <v>427</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E164" s="4">
         <v>814</v>
@@ -9612,7 +9608,7 @@
         <v>428</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C165" s="3" t="s">
         <v>429</v>
@@ -9649,7 +9645,7 @@
         <v>430</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C166" s="3" t="s">
         <v>431</v>
@@ -9686,7 +9682,7 @@
         <v>432</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C167" s="3" t="s">
         <v>433</v>
@@ -9723,7 +9719,7 @@
         <v>435</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C168" s="3" t="s">
         <v>436</v>
@@ -9760,7 +9756,7 @@
         <v>437</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C169" s="3" t="s">
         <v>438</v>
@@ -9797,7 +9793,7 @@
         <v>439</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C170" s="3" t="s">
         <v>440</v>
@@ -9834,7 +9830,7 @@
         <v>441</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C171" s="3" t="s">
         <v>442</v>
@@ -9871,7 +9867,7 @@
         <v>443</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C172" s="3" t="s">
         <v>444</v>
@@ -9908,7 +9904,7 @@
         <v>446</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C173" s="3" t="s">
         <v>447</v>
@@ -9945,13 +9941,13 @@
         <v>448</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C174" s="3" t="s">
         <v>449</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E174" s="4">
         <v>5</v>
@@ -9982,7 +9978,7 @@
         <v>450</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C175" s="3" t="s">
         <v>451</v>
@@ -10019,7 +10015,7 @@
         <v>453</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C176" s="3" t="s">
         <v>454</v>
@@ -10056,7 +10052,7 @@
         <v>455</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C177" s="3" t="s">
         <v>456</v>
@@ -10093,7 +10089,7 @@
         <v>457</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C178" s="3" t="s">
         <v>458</v>
@@ -10130,7 +10126,7 @@
         <v>459</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C179" s="3" t="s">
         <v>460</v>
@@ -10167,13 +10163,13 @@
         <v>461</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C180" s="3" t="s">
         <v>462</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E180" s="4">
         <v>3840</v>
@@ -10204,7 +10200,7 @@
         <v>463</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C181" s="3" t="s">
         <v>464</v>
@@ -10241,7 +10237,7 @@
         <v>466</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C182" s="3" t="s">
         <v>467</v>
@@ -10278,7 +10274,7 @@
         <v>469</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C183" s="3" t="s">
         <v>470</v>
@@ -10315,7 +10311,7 @@
         <v>471</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C184" s="3" t="s">
         <v>472</v>
@@ -10352,7 +10348,7 @@
         <v>473</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C185" s="3" t="s">
         <v>474</v>
@@ -10389,7 +10385,7 @@
         <v>476</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C186" s="3" t="s">
         <v>477</v>
@@ -10426,13 +10422,13 @@
         <v>478</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C187" s="3" t="s">
         <v>479</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E187" s="4">
         <v>192</v>
@@ -10463,7 +10459,7 @@
         <v>480</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C188" s="3" t="s">
         <v>481</v>
@@ -10500,7 +10496,7 @@
         <v>482</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C189" s="3" t="s">
         <v>483</v>
@@ -10537,7 +10533,7 @@
         <v>484</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C190" s="3" t="s">
         <v>485</v>
@@ -10574,7 +10570,7 @@
         <v>486</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C191" s="3" t="s">
         <v>487</v>
@@ -10611,7 +10607,7 @@
         <v>488</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C192" s="3" t="s">
         <v>489</v>
@@ -10648,7 +10644,7 @@
         <v>490</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C193" s="3" t="s">
         <v>491</v>
@@ -10685,7 +10681,7 @@
         <v>492</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C194" s="3" t="s">
         <v>493</v>
@@ -10722,7 +10718,7 @@
         <v>494</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C195" s="3" t="s">
         <v>495</v>
@@ -10759,7 +10755,7 @@
         <v>496</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C196" s="3" t="s">
         <v>497</v>
@@ -10796,13 +10792,13 @@
         <v>498</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C197" s="3" t="s">
         <v>499</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E197" s="4">
         <v>600</v>
@@ -10833,7 +10829,7 @@
         <v>500</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C198" s="3" t="s">
         <v>501</v>
@@ -10870,7 +10866,7 @@
         <v>502</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C199" s="3" t="s">
         <v>503</v>
@@ -10907,13 +10903,13 @@
         <v>504</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C200" s="3" t="s">
         <v>505</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E200" s="4">
         <v>2243</v>
@@ -10944,7 +10940,7 @@
         <v>506</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C201" s="3" t="s">
         <v>507</v>
@@ -10981,7 +10977,7 @@
         <v>508</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C202" s="3" t="s">
         <v>509</v>
@@ -11018,7 +11014,7 @@
         <v>511</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C203" s="3" t="s">
         <v>512</v>
@@ -11055,7 +11051,7 @@
         <v>513</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C204" s="3" t="s">
         <v>514</v>
@@ -11092,7 +11088,7 @@
         <v>515</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C205" s="3" t="s">
         <v>516</v>
@@ -11129,7 +11125,7 @@
         <v>517</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C206" s="3" t="s">
         <v>518</v>
@@ -11166,13 +11162,13 @@
         <v>520</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C207" s="3" t="s">
         <v>521</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E207" s="4">
         <v>516</v>
@@ -11203,7 +11199,7 @@
         <v>522</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C208" s="3" t="s">
         <v>523</v>
@@ -11240,7 +11236,7 @@
         <v>524</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C209" s="3" t="s">
         <v>525</v>
@@ -11277,7 +11273,7 @@
         <v>526</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C210" s="3" t="s">
         <v>527</v>
@@ -11314,7 +11310,7 @@
         <v>528</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C211" s="3" t="s">
         <v>529</v>
@@ -11351,7 +11347,7 @@
         <v>530</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C212" s="3" t="s">
         <v>531</v>
@@ -11388,7 +11384,7 @@
         <v>532</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C213" s="3" t="s">
         <v>533</v>
@@ -11425,7 +11421,7 @@
         <v>534</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C214" s="3" t="s">
         <v>535</v>
@@ -11462,7 +11458,7 @@
         <v>536</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C215" s="3" t="s">
         <v>537</v>
@@ -11499,7 +11495,7 @@
         <v>539</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C216" s="3" t="s">
         <v>540</v>
@@ -11536,7 +11532,7 @@
         <v>541</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C217" s="3" t="s">
         <v>542</v>
@@ -11573,7 +11569,7 @@
         <v>543</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C218" s="3" t="s">
         <v>544</v>
@@ -11610,13 +11606,13 @@
         <v>545</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C219" s="3" t="s">
         <v>546</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E219" s="4">
         <v>938</v>
@@ -11647,13 +11643,13 @@
         <v>547</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C220" s="3" t="s">
         <v>548</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E220" s="4">
         <v>641</v>
@@ -11684,13 +11680,13 @@
         <v>549</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C221" s="3" t="s">
         <v>550</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E221" s="4">
         <v>2242</v>
@@ -11721,7 +11717,7 @@
         <v>551</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C222" s="3" t="s">
         <v>552</v>
@@ -11758,7 +11754,7 @@
         <v>553</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C223" s="3" t="s">
         <v>554</v>
@@ -11795,7 +11791,7 @@
         <v>555</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C224" s="3" t="s">
         <v>556</v>
@@ -11832,7 +11828,7 @@
         <v>557</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C225" s="3" t="s">
         <v>558</v>
@@ -11869,7 +11865,7 @@
         <v>559</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C226" s="3" t="s">
         <v>560</v>
@@ -11906,7 +11902,7 @@
         <v>561</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C227" s="3" t="s">
         <v>562</v>
@@ -11943,7 +11939,7 @@
         <v>563</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C228" s="3" t="s">
         <v>564</v>
@@ -11980,7 +11976,7 @@
         <v>565</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C229" s="3" t="s">
         <v>566</v>
@@ -12017,7 +12013,7 @@
         <v>567</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C230" s="3" t="s">
         <v>568</v>
@@ -12054,7 +12050,7 @@
         <v>569</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C231" s="3" t="s">
         <v>570</v>
@@ -12091,7 +12087,7 @@
         <v>571</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C232" s="3" t="s">
         <v>572</v>
@@ -12128,7 +12124,7 @@
         <v>573</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C233" s="3" t="s">
         <v>574</v>
@@ -12165,13 +12161,13 @@
         <v>575</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C234" s="3" t="s">
         <v>576</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E234" s="4">
         <v>519</v>
@@ -12202,7 +12198,7 @@
         <v>577</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C235" s="3" t="s">
         <v>578</v>
@@ -12239,7 +12235,7 @@
         <v>579</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C236" s="3" t="s">
         <v>580</v>
@@ -12276,7 +12272,7 @@
         <v>581</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C237" s="3" t="s">
         <v>582</v>
@@ -12313,7 +12309,7 @@
         <v>583</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C238" s="3" t="s">
         <v>584</v>
@@ -12350,7 +12346,7 @@
         <v>585</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C239" s="3" t="s">
         <v>586</v>
@@ -12387,7 +12383,7 @@
         <v>587</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C240" s="3" t="s">
         <v>588</v>
@@ -12424,7 +12420,7 @@
         <v>589</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C241" s="3" t="s">
         <v>590</v>
@@ -12461,7 +12457,7 @@
         <v>591</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C242" s="3" t="s">
         <v>592</v>
@@ -12498,7 +12494,7 @@
         <v>593</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C243" s="3" t="s">
         <v>594</v>
@@ -12535,7 +12531,7 @@
         <v>595</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C244" s="3" t="s">
         <v>596</v>
@@ -12572,7 +12568,7 @@
         <v>597</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C245" s="3" t="s">
         <v>598</v>
@@ -12609,7 +12605,7 @@
         <v>599</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C246" s="3" t="s">
         <v>600</v>
@@ -12646,7 +12642,7 @@
         <v>601</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C247" s="3" t="s">
         <v>602</v>
@@ -12683,7 +12679,7 @@
         <v>604</v>
       </c>
       <c r="B248" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C248" s="3" t="s">
         <v>605</v>
@@ -12720,7 +12716,7 @@
         <v>606</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C249" s="3" t="s">
         <v>607</v>
@@ -12757,7 +12753,7 @@
         <v>608</v>
       </c>
       <c r="B250" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C250" s="3" t="s">
         <v>609</v>
@@ -12794,7 +12790,7 @@
         <v>611</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C251" s="3" t="s">
         <v>612</v>
@@ -12831,7 +12827,7 @@
         <v>613</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C252" s="3" t="s">
         <v>614</v>
@@ -12868,13 +12864,13 @@
         <v>615</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C253" s="3" t="s">
         <v>616</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E253" s="4">
         <v>2249</v>
@@ -12905,7 +12901,7 @@
         <v>617</v>
       </c>
       <c r="B254" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C254" s="3" t="s">
         <v>618</v>
@@ -12942,7 +12938,7 @@
         <v>619</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C255" s="3" t="s">
         <v>620</v>
@@ -12979,7 +12975,7 @@
         <v>621</v>
       </c>
       <c r="B256" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C256" s="3" t="s">
         <v>622</v>
@@ -13016,13 +13012,13 @@
         <v>623</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C257" s="3" t="s">
         <v>624</v>
       </c>
       <c r="D257" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E257" s="4">
         <v>1292</v>
@@ -13053,7 +13049,7 @@
         <v>625</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C258" s="3" t="s">
         <v>626</v>
@@ -13090,7 +13086,7 @@
         <v>627</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C259" s="3" t="s">
         <v>628</v>
@@ -13127,7 +13123,7 @@
         <v>629</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C260" s="3" t="s">
         <v>630</v>
@@ -13164,7 +13160,7 @@
         <v>632</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C261" s="3" t="s">
         <v>633</v>
@@ -13201,7 +13197,7 @@
         <v>634</v>
       </c>
       <c r="B262" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C262" s="3" t="s">
         <v>635</v>
@@ -13238,7 +13234,7 @@
         <v>636</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C263" s="3" t="s">
         <v>637</v>
@@ -13275,7 +13271,7 @@
         <v>638</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C264" s="3" t="s">
         <v>639</v>
@@ -13312,7 +13308,7 @@
         <v>640</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C265" s="3" t="s">
         <v>641</v>
@@ -13349,7 +13345,7 @@
         <v>642</v>
       </c>
       <c r="B266" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C266" s="3" t="s">
         <v>643</v>
@@ -13386,7 +13382,7 @@
         <v>644</v>
       </c>
       <c r="B267" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C267" s="3" t="s">
         <v>645</v>
@@ -13423,7 +13419,7 @@
         <v>646</v>
       </c>
       <c r="B268" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C268" s="3" t="s">
         <v>647</v>
@@ -13460,7 +13456,7 @@
         <v>648</v>
       </c>
       <c r="B269" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C269" s="3" t="s">
         <v>649</v>
@@ -13497,7 +13493,7 @@
         <v>650</v>
       </c>
       <c r="B270" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C270" s="3" t="s">
         <v>651</v>
@@ -13534,7 +13530,7 @@
         <v>652</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C271" s="3" t="s">
         <v>653</v>
@@ -13571,7 +13567,7 @@
         <v>654</v>
       </c>
       <c r="B272" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C272" s="3" t="s">
         <v>655</v>
@@ -13608,7 +13604,7 @@
         <v>656</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C273" s="3" t="s">
         <v>657</v>
@@ -13645,7 +13641,7 @@
         <v>658</v>
       </c>
       <c r="B274" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C274" s="3" t="s">
         <v>659</v>
@@ -13682,7 +13678,7 @@
         <v>660</v>
       </c>
       <c r="B275" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C275" s="3" t="s">
         <v>661</v>
@@ -13719,7 +13715,7 @@
         <v>662</v>
       </c>
       <c r="B276" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C276" s="3" t="s">
         <v>663</v>
@@ -13756,7 +13752,7 @@
         <v>664</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C277" s="3" t="s">
         <v>665</v>
@@ -13793,7 +13789,7 @@
         <v>666</v>
       </c>
       <c r="B278" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C278" s="3" t="s">
         <v>667</v>
@@ -13830,7 +13826,7 @@
         <v>668</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C279" s="3" t="s">
         <v>669</v>
@@ -13867,7 +13863,7 @@
         <v>670</v>
       </c>
       <c r="B280" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C280" s="3" t="s">
         <v>671</v>
@@ -13904,13 +13900,13 @@
         <v>672</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C281" s="3" t="s">
         <v>673</v>
       </c>
       <c r="D281" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E281" s="4">
         <v>1920</v>
@@ -13941,7 +13937,7 @@
         <v>674</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C282" s="3" t="s">
         <v>675</v>
@@ -13978,7 +13974,7 @@
         <v>676</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C283" s="3" t="s">
         <v>677</v>
@@ -14015,7 +14011,7 @@
         <v>678</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C284" s="3" t="s">
         <v>679</v>
@@ -14052,7 +14048,7 @@
         <v>680</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C285" s="3" t="s">
         <v>681</v>
@@ -14089,7 +14085,7 @@
         <v>682</v>
       </c>
       <c r="B286" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C286" s="3" t="s">
         <v>683</v>
@@ -14126,7 +14122,7 @@
         <v>685</v>
       </c>
       <c r="B287" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C287" s="3" t="s">
         <v>686</v>
@@ -14163,13 +14159,13 @@
         <v>687</v>
       </c>
       <c r="B288" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C288" s="3" t="s">
         <v>688</v>
       </c>
       <c r="D288" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E288" s="4">
         <v>642</v>
@@ -14200,7 +14196,7 @@
         <v>689</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C289" s="3" t="s">
         <v>690</v>
@@ -14237,7 +14233,7 @@
         <v>691</v>
       </c>
       <c r="B290" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C290" s="3" t="s">
         <v>692</v>
@@ -14274,7 +14270,7 @@
         <v>693</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C291" s="3" t="s">
         <v>694</v>
@@ -14311,7 +14307,7 @@
         <v>695</v>
       </c>
       <c r="B292" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C292" s="3" t="s">
         <v>696</v>
@@ -14348,7 +14344,7 @@
         <v>697</v>
       </c>
       <c r="B293" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C293" s="3" t="s">
         <v>698</v>
@@ -14385,7 +14381,7 @@
         <v>699</v>
       </c>
       <c r="B294" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C294" s="3" t="s">
         <v>700</v>
@@ -14422,7 +14418,7 @@
         <v>701</v>
       </c>
       <c r="B295" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C295" s="3" t="s">
         <v>702</v>
@@ -14459,7 +14455,7 @@
         <v>704</v>
       </c>
       <c r="B296" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C296" s="3" t="s">
         <v>705</v>
@@ -14496,7 +14492,7 @@
         <v>706</v>
       </c>
       <c r="B297" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C297" s="3" t="s">
         <v>707</v>
@@ -14533,7 +14529,7 @@
         <v>708</v>
       </c>
       <c r="B298" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C298" s="3" t="s">
         <v>709</v>
@@ -14570,7 +14566,7 @@
         <v>711</v>
       </c>
       <c r="B299" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C299" s="3" t="s">
         <v>712</v>
@@ -14607,7 +14603,7 @@
         <v>713</v>
       </c>
       <c r="B300" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C300" s="3" t="s">
         <v>714</v>
@@ -14644,7 +14640,7 @@
         <v>716</v>
       </c>
       <c r="B301" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C301" s="3" t="s">
         <v>717</v>
@@ -14681,7 +14677,7 @@
         <v>718</v>
       </c>
       <c r="B302" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C302" s="3" t="s">
         <v>719</v>
@@ -14718,7 +14714,7 @@
         <v>720</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C303" s="3" t="s">
         <v>721</v>
@@ -14755,13 +14751,13 @@
         <v>722</v>
       </c>
       <c r="B304" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C304" s="3" t="s">
         <v>723</v>
       </c>
       <c r="D304" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E304" s="4">
         <v>1282</v>
@@ -14792,7 +14788,7 @@
         <v>724</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C305" s="3" t="s">
         <v>725</v>
@@ -14829,7 +14825,7 @@
         <v>727</v>
       </c>
       <c r="B306" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C306" s="3" t="s">
         <v>728</v>
@@ -14866,7 +14862,7 @@
         <v>730</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C307" s="3" t="s">
         <v>731</v>
@@ -14903,7 +14899,7 @@
         <v>732</v>
       </c>
       <c r="B308" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C308" s="3" t="s">
         <v>733</v>
@@ -14940,7 +14936,7 @@
         <v>734</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C309" s="3" t="s">
         <v>735</v>
@@ -14977,7 +14973,7 @@
         <v>736</v>
       </c>
       <c r="B310" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C310" s="3" t="s">
         <v>737</v>
@@ -15014,7 +15010,7 @@
         <v>738</v>
       </c>
       <c r="B311" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C311" s="3" t="s">
         <v>739</v>
@@ -15051,7 +15047,7 @@
         <v>740</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C312" s="3" t="s">
         <v>741</v>
@@ -15088,7 +15084,7 @@
         <v>742</v>
       </c>
       <c r="B313" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C313" s="3" t="s">
         <v>743</v>
@@ -15125,13 +15121,13 @@
         <v>744</v>
       </c>
       <c r="B314" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C314" s="3" t="s">
         <v>745</v>
       </c>
       <c r="D314" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E314" s="4">
         <v>962</v>
@@ -15162,7 +15158,7 @@
         <v>746</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C315" s="3" t="s">
         <v>747</v>
@@ -15199,7 +15195,7 @@
         <v>748</v>
       </c>
       <c r="B316" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C316" s="3" t="s">
         <v>749</v>
@@ -15236,7 +15232,7 @@
         <v>750</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C317" s="3" t="s">
         <v>751</v>
@@ -15273,7 +15269,7 @@
         <v>752</v>
       </c>
       <c r="B318" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C318" s="3" t="s">
         <v>753</v>
@@ -15310,7 +15306,7 @@
         <v>754</v>
       </c>
       <c r="B319" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C319" s="3" t="s">
         <v>755</v>
@@ -15347,7 +15343,7 @@
         <v>756</v>
       </c>
       <c r="B320" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C320" s="3" t="s">
         <v>757</v>
@@ -15384,7 +15380,7 @@
         <v>758</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C321" s="3" t="s">
         <v>759</v>
@@ -15421,7 +15417,7 @@
         <v>760</v>
       </c>
       <c r="B322" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C322" s="3" t="s">
         <v>761</v>
@@ -15458,7 +15454,7 @@
         <v>762</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C323" s="3" t="s">
         <v>763</v>
@@ -15495,7 +15491,7 @@
         <v>764</v>
       </c>
       <c r="B324" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C324" s="3" t="s">
         <v>765</v>
@@ -15532,7 +15528,7 @@
         <v>766</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C325" s="3" t="s">
         <v>767</v>
@@ -15569,7 +15565,7 @@
         <v>768</v>
       </c>
       <c r="B326" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C326" s="3" t="s">
         <v>769</v>
@@ -15606,7 +15602,7 @@
         <v>770</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C327" s="3" t="s">
         <v>771</v>
@@ -15643,7 +15639,7 @@
         <v>772</v>
       </c>
       <c r="B328" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C328" s="3" t="s">
         <v>773</v>
@@ -15680,7 +15676,7 @@
         <v>774</v>
       </c>
       <c r="B329" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C329" s="3" t="s">
         <v>775</v>
@@ -15717,7 +15713,7 @@
         <v>776</v>
       </c>
       <c r="B330" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C330" s="3" t="s">
         <v>777</v>
@@ -15754,7 +15750,7 @@
         <v>778</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C331" s="3" t="s">
         <v>779</v>
@@ -15791,7 +15787,7 @@
         <v>780</v>
       </c>
       <c r="B332" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C332" s="3" t="s">
         <v>781</v>
@@ -15828,7 +15824,7 @@
         <v>782</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C333" s="3" t="s">
         <v>783</v>
@@ -15865,7 +15861,7 @@
         <v>784</v>
       </c>
       <c r="B334" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C334" s="3" t="s">
         <v>785</v>
@@ -15902,7 +15898,7 @@
         <v>786</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C335" s="3" t="s">
         <v>787</v>
@@ -15939,7 +15935,7 @@
         <v>788</v>
       </c>
       <c r="B336" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C336" s="3" t="s">
         <v>789</v>
@@ -15976,7 +15972,7 @@
         <v>790</v>
       </c>
       <c r="B337" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C337" s="3" t="s">
         <v>791</v>
@@ -16013,7 +16009,7 @@
         <v>792</v>
       </c>
       <c r="B338" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C338" s="3" t="s">
         <v>793</v>
@@ -16050,7 +16046,7 @@
         <v>795</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C339" s="3" t="s">
         <v>796</v>
@@ -16087,13 +16083,13 @@
         <v>797</v>
       </c>
       <c r="B340" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C340" s="3" t="s">
         <v>798</v>
       </c>
       <c r="D340" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E340" s="4">
         <v>550</v>
@@ -16124,7 +16120,7 @@
         <v>799</v>
       </c>
       <c r="B341" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C341" s="3" t="s">
         <v>800</v>
@@ -16161,7 +16157,7 @@
         <v>802</v>
       </c>
       <c r="B342" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C342" s="3" t="s">
         <v>803</v>
@@ -16198,7 +16194,7 @@
         <v>805</v>
       </c>
       <c r="B343" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C343" s="3" t="s">
         <v>806</v>
@@ -16235,7 +16231,7 @@
         <v>807</v>
       </c>
       <c r="B344" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C344" s="3" t="s">
         <v>808</v>
@@ -16272,7 +16268,7 @@
         <v>809</v>
       </c>
       <c r="B345" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C345" s="3" t="s">
         <v>810</v>
@@ -16309,7 +16305,7 @@
         <v>812</v>
       </c>
       <c r="B346" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C346" s="3" t="s">
         <v>813</v>
@@ -16346,7 +16342,7 @@
         <v>815</v>
       </c>
       <c r="B347" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C347" s="3" t="s">
         <v>816</v>
@@ -16383,7 +16379,7 @@
         <v>817</v>
       </c>
       <c r="B348" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C348" s="3" t="s">
         <v>818</v>
@@ -16420,13 +16416,13 @@
         <v>819</v>
       </c>
       <c r="B349" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C349" s="3" t="s">
         <v>820</v>
       </c>
       <c r="D349" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E349" s="4">
         <v>2560</v>
@@ -16457,7 +16453,7 @@
         <v>821</v>
       </c>
       <c r="B350" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C350" s="3" t="s">
         <v>822</v>
@@ -16494,7 +16490,7 @@
         <v>823</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C351" s="3" t="s">
         <v>824</v>
@@ -16531,7 +16527,7 @@
         <v>825</v>
       </c>
       <c r="B352" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C352" s="3" t="s">
         <v>826</v>
@@ -16568,7 +16564,7 @@
         <v>827</v>
       </c>
       <c r="B353" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C353" s="3" t="s">
         <v>828</v>
@@ -16605,7 +16601,7 @@
         <v>829</v>
       </c>
       <c r="B354" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C354" s="3" t="s">
         <v>830</v>
@@ -16642,7 +16638,7 @@
         <v>831</v>
       </c>
       <c r="B355" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C355" s="3" t="s">
         <v>832</v>
@@ -16679,7 +16675,7 @@
         <v>833</v>
       </c>
       <c r="B356" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C356" s="3" t="s">
         <v>834</v>
@@ -16716,7 +16712,7 @@
         <v>835</v>
       </c>
       <c r="B357" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C357" s="3" t="s">
         <v>836</v>
@@ -16753,7 +16749,7 @@
         <v>837</v>
       </c>
       <c r="B358" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C358" s="3" t="s">
         <v>838</v>
@@ -16790,7 +16786,7 @@
         <v>839</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C359" s="3" t="s">
         <v>840</v>
@@ -16827,13 +16823,13 @@
         <v>841</v>
       </c>
       <c r="B360" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C360" s="3" t="s">
         <v>842</v>
       </c>
       <c r="D360" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E360" s="4">
         <v>800</v>
@@ -16864,7 +16860,7 @@
         <v>843</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C361" s="3" t="s">
         <v>844</v>
@@ -16901,7 +16897,7 @@
         <v>845</v>
       </c>
       <c r="B362" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C362" s="3" t="s">
         <v>846</v>
@@ -16938,7 +16934,7 @@
         <v>847</v>
       </c>
       <c r="B363" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C363" s="3" t="s">
         <v>848</v>
@@ -16975,7 +16971,7 @@
         <v>850</v>
       </c>
       <c r="B364" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C364" s="3" t="s">
         <v>851</v>
@@ -17012,7 +17008,7 @@
         <v>852</v>
       </c>
       <c r="B365" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C365" s="3" t="s">
         <v>853</v>
@@ -17049,13 +17045,13 @@
         <v>854</v>
       </c>
       <c r="B366" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C366" s="3" t="s">
         <v>855</v>
       </c>
       <c r="D366" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E366" s="4">
         <v>545</v>
@@ -17086,7 +17082,7 @@
         <v>856</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C367" s="3" t="s">
         <v>857</v>
@@ -17123,7 +17119,7 @@
         <v>858</v>
       </c>
       <c r="B368" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C368" s="3" t="s">
         <v>859</v>
@@ -17160,7 +17156,7 @@
         <v>860</v>
       </c>
       <c r="B369" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C369" s="3" t="s">
         <v>861</v>
@@ -17197,7 +17193,7 @@
         <v>862</v>
       </c>
       <c r="B370" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C370" s="3" t="s">
         <v>863</v>
@@ -17234,7 +17230,7 @@
         <v>864</v>
       </c>
       <c r="B371" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C371" s="3" t="s">
         <v>865</v>
@@ -17271,7 +17267,7 @@
         <v>866</v>
       </c>
       <c r="B372" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C372" s="3" t="s">
         <v>867</v>
@@ -17308,7 +17304,7 @@
         <v>868</v>
       </c>
       <c r="B373" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C373" s="3" t="s">
         <v>869</v>
@@ -17345,7 +17341,7 @@
         <v>870</v>
       </c>
       <c r="B374" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C374" s="3" t="s">
         <v>871</v>
@@ -17382,7 +17378,7 @@
         <v>873</v>
       </c>
       <c r="B375" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C375" s="3" t="s">
         <v>874</v>
@@ -17419,7 +17415,7 @@
         <v>875</v>
       </c>
       <c r="B376" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C376" s="3" t="s">
         <v>876</v>
@@ -17456,7 +17452,7 @@
         <v>878</v>
       </c>
       <c r="B377" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C377" s="3" t="s">
         <v>879</v>
@@ -17493,7 +17489,7 @@
         <v>880</v>
       </c>
       <c r="B378" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C378" s="3" t="s">
         <v>881</v>
@@ -17530,7 +17526,7 @@
         <v>882</v>
       </c>
       <c r="B379" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C379" s="3" t="s">
         <v>883</v>
@@ -17567,7 +17563,7 @@
         <v>884</v>
       </c>
       <c r="B380" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C380" s="3" t="s">
         <v>885</v>
@@ -17604,7 +17600,7 @@
         <v>886</v>
       </c>
       <c r="B381" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C381" s="3" t="s">
         <v>887</v>
@@ -17641,7 +17637,7 @@
         <v>888</v>
       </c>
       <c r="B382" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C382" s="3" t="s">
         <v>889</v>
@@ -17678,7 +17674,7 @@
         <v>890</v>
       </c>
       <c r="B383" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C383" s="3" t="s">
         <v>891</v>
@@ -17715,7 +17711,7 @@
         <v>892</v>
       </c>
       <c r="B384" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C384" s="3" t="s">
         <v>893</v>
@@ -17752,7 +17748,7 @@
         <v>894</v>
       </c>
       <c r="B385" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C385" s="3" t="s">
         <v>895</v>
@@ -17789,13 +17785,13 @@
         <v>896</v>
       </c>
       <c r="B386" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C386" s="3" t="s">
         <v>897</v>
       </c>
       <c r="D386" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E386" s="4">
         <v>2560</v>
@@ -17826,7 +17822,7 @@
         <v>898</v>
       </c>
       <c r="B387" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C387" s="3" t="s">
         <v>899</v>
@@ -17863,7 +17859,7 @@
         <v>900</v>
       </c>
       <c r="B388" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C388" s="3" t="s">
         <v>901</v>
@@ -17900,7 +17896,7 @@
         <v>902</v>
       </c>
       <c r="B389" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C389" s="3" t="s">
         <v>903</v>
@@ -17937,7 +17933,7 @@
         <v>904</v>
       </c>
       <c r="B390" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C390" s="3" t="s">
         <v>905</v>
@@ -17974,7 +17970,7 @@
         <v>907</v>
       </c>
       <c r="B391" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C391" s="3" t="s">
         <v>908</v>
@@ -18011,7 +18007,7 @@
         <v>909</v>
       </c>
       <c r="B392" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C392" s="3" t="s">
         <v>910</v>
@@ -18048,7 +18044,7 @@
         <v>911</v>
       </c>
       <c r="B393" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C393" s="3" t="s">
         <v>912</v>
@@ -18085,13 +18081,13 @@
         <v>913</v>
       </c>
       <c r="B394" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C394" s="3" t="s">
         <v>914</v>
       </c>
       <c r="D394" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E394" s="4">
         <v>378</v>
@@ -18122,7 +18118,7 @@
         <v>915</v>
       </c>
       <c r="B395" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C395" s="3" t="s">
         <v>916</v>
@@ -18159,7 +18155,7 @@
         <v>917</v>
       </c>
       <c r="B396" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C396" s="3" t="s">
         <v>918</v>
@@ -18196,7 +18192,7 @@
         <v>919</v>
       </c>
       <c r="B397" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C397" s="3" t="s">
         <v>920</v>
@@ -18233,7 +18229,7 @@
         <v>921</v>
       </c>
       <c r="B398" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C398" s="3" t="s">
         <v>922</v>
@@ -18270,7 +18266,7 @@
         <v>923</v>
       </c>
       <c r="B399" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C399" s="3" t="s">
         <v>924</v>
@@ -18307,13 +18303,13 @@
         <v>925</v>
       </c>
       <c r="B400" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C400" s="3" t="s">
         <v>926</v>
       </c>
       <c r="D400" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E400" s="4">
         <v>544</v>
@@ -18344,13 +18340,13 @@
         <v>927</v>
       </c>
       <c r="B401" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C401" s="3" t="s">
         <v>928</v>
       </c>
       <c r="D401" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E401" s="4">
         <v>800</v>
@@ -18381,7 +18377,7 @@
         <v>929</v>
       </c>
       <c r="B402" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C402" s="3" t="s">
         <v>930</v>
@@ -18418,7 +18414,7 @@
         <v>931</v>
       </c>
       <c r="B403" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C403" s="3" t="s">
         <v>932</v>
@@ -18455,7 +18451,7 @@
         <v>933</v>
       </c>
       <c r="B404" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C404" s="3" t="s">
         <v>934</v>
@@ -18492,7 +18488,7 @@
         <v>935</v>
       </c>
       <c r="B405" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C405" s="3" t="s">
         <v>936</v>
@@ -18529,7 +18525,7 @@
         <v>937</v>
       </c>
       <c r="B406" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C406" s="3" t="s">
         <v>938</v>
@@ -18566,7 +18562,7 @@
         <v>939</v>
       </c>
       <c r="B407" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C407" s="3" t="s">
         <v>940</v>
@@ -18603,7 +18599,7 @@
         <v>941</v>
       </c>
       <c r="B408" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C408" s="3" t="s">
         <v>942</v>
@@ -18640,7 +18636,7 @@
         <v>943</v>
       </c>
       <c r="B409" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C409" s="3" t="s">
         <v>944</v>
@@ -18677,7 +18673,7 @@
         <v>945</v>
       </c>
       <c r="B410" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C410" s="3" t="s">
         <v>946</v>
@@ -18714,13 +18710,13 @@
         <v>947</v>
       </c>
       <c r="B411" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C411" s="3" t="s">
         <v>948</v>
       </c>
       <c r="D411" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E411" s="4">
         <v>620</v>
@@ -18751,7 +18747,7 @@
         <v>949</v>
       </c>
       <c r="B412" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C412" s="3" t="s">
         <v>950</v>
@@ -18788,7 +18784,7 @@
         <v>951</v>
       </c>
       <c r="B413" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C413" s="3" t="s">
         <v>952</v>
@@ -18825,7 +18821,7 @@
         <v>953</v>
       </c>
       <c r="B414" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C414" s="3" t="s">
         <v>954</v>
@@ -18862,7 +18858,7 @@
         <v>955</v>
       </c>
       <c r="B415" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C415" s="3" t="s">
         <v>956</v>
@@ -18899,7 +18895,7 @@
         <v>957</v>
       </c>
       <c r="B416" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C416" s="3" t="s">
         <v>958</v>
@@ -18936,7 +18932,7 @@
         <v>959</v>
       </c>
       <c r="B417" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C417" s="3" t="s">
         <v>960</v>
@@ -18973,7 +18969,7 @@
         <v>961</v>
       </c>
       <c r="B418" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C418" s="3" t="s">
         <v>962</v>
@@ -19010,13 +19006,13 @@
         <v>963</v>
       </c>
       <c r="B419" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C419" s="3" t="s">
         <v>964</v>
       </c>
       <c r="D419" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E419" s="4">
         <v>131</v>
@@ -19047,13 +19043,13 @@
         <v>965</v>
       </c>
       <c r="B420" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C420" s="3" t="s">
         <v>966</v>
       </c>
       <c r="D420" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E420" s="4">
         <v>76</v>
@@ -19084,7 +19080,7 @@
         <v>967</v>
       </c>
       <c r="B421" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C421" s="3" t="s">
         <v>968</v>
@@ -19121,7 +19117,7 @@
         <v>969</v>
       </c>
       <c r="B422" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C422" s="3" t="s">
         <v>970</v>
@@ -19158,7 +19154,7 @@
         <v>971</v>
       </c>
       <c r="B423" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C423" s="3" t="s">
         <v>972</v>
@@ -19195,7 +19191,7 @@
         <v>973</v>
       </c>
       <c r="B424" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C424" s="3" t="s">
         <v>974</v>
@@ -19232,7 +19228,7 @@
         <v>975</v>
       </c>
       <c r="B425" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C425" s="3" t="s">
         <v>976</v>
@@ -19269,7 +19265,7 @@
         <v>977</v>
       </c>
       <c r="B426" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C426" s="3" t="s">
         <v>978</v>
@@ -19306,7 +19302,7 @@
         <v>979</v>
       </c>
       <c r="B427" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C427" s="3" t="s">
         <v>980</v>
@@ -19343,7 +19339,7 @@
         <v>981</v>
       </c>
       <c r="B428" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C428" s="3" t="s">
         <v>982</v>
@@ -19380,7 +19376,7 @@
         <v>983</v>
       </c>
       <c r="B429" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C429" s="3" t="s">
         <v>984</v>
@@ -19417,7 +19413,7 @@
         <v>985</v>
       </c>
       <c r="B430" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C430" s="3" t="s">
         <v>986</v>
@@ -19454,7 +19450,7 @@
         <v>987</v>
       </c>
       <c r="B431" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C431" s="3" t="s">
         <v>988</v>
@@ -19491,7 +19487,7 @@
         <v>989</v>
       </c>
       <c r="B432" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C432" s="3" t="s">
         <v>990</v>
@@ -19528,7 +19524,7 @@
         <v>991</v>
       </c>
       <c r="B433" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C433" s="3" t="s">
         <v>992</v>
@@ -19565,7 +19561,7 @@
         <v>993</v>
       </c>
       <c r="B434" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C434" s="3" t="s">
         <v>994</v>
@@ -19602,7 +19598,7 @@
         <v>995</v>
       </c>
       <c r="B435" s="3" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C435" s="3" t="s">
         <v>996</v>
@@ -19645,16 +19641,16 @@
         <v>5060563.5</v>
       </c>
       <c r="G436" s="7">
-        <v>4757418.5</v>
+        <v>4760383.5</v>
       </c>
       <c r="H436" s="6">
-        <v>178413</v>
+        <v>178692</v>
       </c>
       <c r="I436" s="7">
-        <v>4609888.959</v>
+        <v>4617218.419</v>
       </c>
       <c r="J436" s="6">
-        <v>17631</v>
+        <v>17352</v>
       </c>
     </row>
   </sheetData>
